--- a/04_DESIGN_TABLES/DesignTable_1404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1404_SW2.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="C2" t="n">
-        <v>0.54271</v>
+        <v>0.57735</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0.40779</v>
@@ -721,7 +721,7 @@
         <v>0.35064</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="O2" t="n">
         <v>0.304</v>
@@ -769,7 +769,7 @@
         <v>0.281</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AE2" t="n">
         <v>0.759</v>
@@ -787,7 +787,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AK2" t="n">
         <v>0.53</v>
@@ -796,7 +796,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AN2" t="n">
         <v>0.6899999999999999</v>
@@ -845,12 +845,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051)</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -869,10 +869,10 @@
         <v>1.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28868</v>
+        <v>0.32447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>0.19657</v>
@@ -977,7 +977,7 @@
         <v>0.55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AN3" t="n">
         <v>0.47</v>
@@ -1026,7 +1026,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1042,13 +1047,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36373</v>
+        <v>0.39722</v>
       </c>
       <c r="D4" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.19657</v>
@@ -1078,7 +1083,7 @@
         <v>0.16694</v>
       </c>
       <c r="N4" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="O4" t="n">
         <v>0.1825</v>
@@ -1126,7 +1131,7 @@
         <v>0.1485</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AE4" t="n">
         <v>0.481</v>
@@ -1144,7 +1149,7 @@
         <v>0.28494</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
         <v>0.19</v>
@@ -1153,7 +1158,7 @@
         <v>0.525</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="AN4" t="n">
         <v>0.555</v>
@@ -1202,7 +1207,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051)</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1218,13 +1228,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="C5" t="n">
-        <v>0.36373</v>
+        <v>0.39722</v>
       </c>
       <c r="D5" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.26092</v>
@@ -1254,7 +1264,7 @@
         <v>0.21647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="O5" t="n">
         <v>0.129</v>
@@ -1302,7 +1312,7 @@
         <v>0.117</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AE5" t="n">
         <v>0.364</v>
@@ -1320,7 +1330,7 @@
         <v>0.21163</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
         <v>0.28</v>
@@ -1378,7 +1388,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051)</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1397,10 +1412,10 @@
         <v>1.44</v>
       </c>
       <c r="C6" t="n">
-        <v>0.36373</v>
+        <v>0.39722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.63</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.26092</v>
@@ -1505,7 +1520,7 @@
         <v>0.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AN6" t="n">
         <v>0.5600000000000001</v>
@@ -1554,7 +1569,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1570,7 +1590,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="C7" t="n">
         <v>0.46765</v>
@@ -1606,7 +1626,7 @@
         <v>0.21647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
         <v>0.2465</v>
@@ -1654,7 +1674,7 @@
         <v>0.211</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="AE7" t="n">
         <v>0.612</v>
@@ -1672,7 +1692,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AK7" t="n">
         <v>0.28</v>
@@ -1735,7 +1755,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length)</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1751,13 +1771,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.54271</v>
+        <v>0.57735</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0.26092</v>
@@ -1787,7 +1807,7 @@
         <v>0.21647</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="O8" t="n">
         <v>0.304</v>
@@ -1835,7 +1855,7 @@
         <v>0.281</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AE8" t="n">
         <v>0.759</v>
@@ -1853,7 +1873,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AK8" t="n">
         <v>0.28</v>
@@ -1862,7 +1882,7 @@
         <v>0.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="AN8" t="n">
         <v>0.6899999999999999</v>
@@ -1911,12 +1931,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051)</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -1932,7 +1952,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="C9" t="n">
         <v>0.43301</v>
@@ -1968,7 +1988,7 @@
         <v>0.28378</v>
       </c>
       <c r="N9" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="O9" t="n">
         <v>0.1825</v>
@@ -2016,7 +2036,7 @@
         <v>0.1485</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AE9" t="n">
         <v>0.481</v>
@@ -2034,7 +2054,7 @@
         <v>0.28494</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AK9" t="n">
         <v>0.41</v>
@@ -2043,7 +2063,7 @@
         <v>0.74</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AN9" t="n">
         <v>0.59</v>
@@ -2093,6 +2113,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2108,13 +2133,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.46765</v>
+        <v>0.50518</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="E10" t="n">
         <v>0.32823</v>
@@ -2144,7 +2169,7 @@
         <v>0.28378</v>
       </c>
       <c r="N10" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="O10" t="n">
         <v>0.2465</v>
@@ -2192,7 +2217,7 @@
         <v>0.211</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="AE10" t="n">
         <v>0.612</v>
@@ -2210,7 +2235,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AK10" t="n">
         <v>0.41</v>
@@ -2219,7 +2244,7 @@
         <v>0.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
         <v>0.6</v>
@@ -2268,12 +2293,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051)</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -2289,13 +2314,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="C11" t="n">
-        <v>0.54271</v>
+        <v>0.57735</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0.32823</v>
@@ -2325,7 +2350,7 @@
         <v>0.28378</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="O11" t="n">
         <v>0.304</v>
@@ -2373,7 +2398,7 @@
         <v>0.281</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AE11" t="n">
         <v>0.759</v>
@@ -2391,7 +2416,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AK11" t="n">
         <v>0.41</v>
@@ -2400,7 +2425,7 @@
         <v>0.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AN11" t="n">
         <v>0.6899999999999999</v>
@@ -2449,12 +2474,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051)</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -2470,7 +2495,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="C12" t="n">
         <v>0.50807</v>
@@ -2506,7 +2531,7 @@
         <v>0.35064</v>
       </c>
       <c r="N12" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="O12" t="n">
         <v>0.2465</v>
@@ -2554,7 +2579,7 @@
         <v>0.211</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="AE12" t="n">
         <v>0.612</v>
@@ -2572,7 +2597,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AK12" t="n">
         <v>0.53</v>
@@ -2581,7 +2606,7 @@
         <v>0.95</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
         <v>0.63</v>
@@ -2635,7 +2660,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -2651,13 +2676,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65241</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
         <v>0.40779</v>
@@ -2687,7 +2712,7 @@
         <v>0.35064</v>
       </c>
       <c r="N13" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0.389</v>
@@ -2735,7 +2760,7 @@
         <v>0.375</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="AE13" t="n">
         <v>0.97</v>
@@ -2753,7 +2778,7 @@
         <v>0.54214</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AK13" t="n">
         <v>0.53</v>
@@ -2762,7 +2787,7 @@
         <v>1.015</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="AN13" t="n">
         <v>0.735</v>
@@ -2811,7 +2836,12 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051) | Air-Way nut face to stem tip (W-L) 0.360 vs Brennan 0.330: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -2827,7 +2857,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2863,7 +2893,7 @@
         <v>0.45527</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="O14" t="n">
         <v>0.304</v>
@@ -2911,7 +2941,7 @@
         <v>0.281</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AE14" t="n">
         <v>0.759</v>
@@ -2929,7 +2959,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AK14" t="n">
         <v>0.72</v>
@@ -2938,7 +2968,7 @@
         <v>0.945</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AN14" t="n">
         <v>0.695</v>
@@ -2992,7 +3022,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | Air-Way nut face to stem tip (W-L) 0.310 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -3008,13 +3038,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.65241</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0.51241</v>
@@ -3044,7 +3074,7 @@
         <v>0.45527</v>
       </c>
       <c r="N15" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="O15" t="n">
         <v>0.389</v>
@@ -3092,7 +3122,7 @@
         <v>0.375</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AE15" t="n">
         <v>0.97</v>
@@ -3110,16 +3140,16 @@
         <v>0.54214</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="AL15" t="n">
         <v>1.015</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="AN15" t="n">
         <v>0.735</v>
@@ -3168,7 +3198,12 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051) | Air-Way nut face to stem tip (W-L) 0.370 vs Brennan 0.330: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -3184,7 +3219,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="C16" t="n">
         <v>0.86603</v>
@@ -3220,7 +3255,7 @@
         <v>0.45527</v>
       </c>
       <c r="N16" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
         <v>0.525</v>
@@ -3268,7 +3303,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AE16" t="n">
         <v>1.211</v>
@@ -3286,7 +3321,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AK16" t="n">
         <v>0.72</v>
@@ -3295,7 +3330,7 @@
         <v>0.985</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AN16" t="n">
         <v>0.845</v>
@@ -3349,7 +3384,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.370 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -3368,10 +3403,10 @@
         <v>2.31</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79674</v>
+        <v>0.86603</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>0.6415999999999999</v>
@@ -3476,7 +3511,7 @@
         <v>1.235</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="AN17" t="n">
         <v>0.765</v>
@@ -3525,7 +3560,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -3541,7 +3581,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="C18" t="n">
         <v>0.86603</v>
@@ -3577,7 +3617,7 @@
         <v>0.57203</v>
       </c>
       <c r="N18" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>0.525</v>
@@ -3625,7 +3665,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="AE18" t="n">
         <v>1.211</v>
@@ -3643,7 +3683,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AK18" t="n">
         <v>0.9399999999999999</v>
@@ -3652,7 +3692,7 @@
         <v>1.175</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AN18" t="n">
         <v>0.845</v>
@@ -3706,7 +3746,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -3722,13 +3762,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="C19" t="n">
-        <v>1.01036</v>
+        <v>1.08253</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E19" t="n">
         <v>0.6415999999999999</v>
@@ -3758,7 +3798,7 @@
         <v>0.57203</v>
       </c>
       <c r="N19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="O19" t="n">
         <v>0.695</v>
@@ -3806,7 +3846,7 @@
         <v>0.6405</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="AE19" t="n">
         <v>1.555</v>
@@ -3824,7 +3864,7 @@
         <v>0.84707</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AK19" t="n">
         <v>0.9399999999999999</v>
@@ -3882,7 +3922,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051) | Air-Way nut face to stem tip (W-L) 0.440 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -3898,13 +3943,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="C20" t="n">
-        <v>1.01036</v>
+        <v>1.08253</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E20" t="n">
         <v>0.81335</v>
@@ -3934,7 +3979,7 @@
         <v>0.74378</v>
       </c>
       <c r="N20" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="O20" t="n">
         <v>0.525</v>
@@ -3982,7 +4027,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="AE20" t="n">
         <v>1.211</v>
@@ -4000,7 +4045,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" t="n">
         <v>1.25</v>
@@ -4009,7 +4054,7 @@
         <v>1.19</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AN20" t="n">
         <v>0.83</v>
@@ -4058,12 +4103,12 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051) | Air-Way nut face to stem tip (W-L) 0.400 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -4079,13 +4124,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="C21" t="n">
-        <v>1.01036</v>
+        <v>1.08253</v>
       </c>
       <c r="D21" t="n">
-        <v>1.75</v>
+        <v>1.875</v>
       </c>
       <c r="E21" t="n">
         <v>0.81335</v>
@@ -4115,7 +4160,7 @@
         <v>0.74378</v>
       </c>
       <c r="N21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="O21" t="n">
         <v>0.695</v>
@@ -4163,7 +4208,7 @@
         <v>0.6405</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="AE21" t="n">
         <v>1.555</v>
@@ -4181,7 +4226,7 @@
         <v>0.84707</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AK21" t="n">
         <v>1.25</v>
@@ -4239,7 +4284,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051) | Air-Way nut face to stem tip (W-L) 0.460 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -4418,6 +4468,11 @@
           <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.51 -&gt; OMi 2.47 (Items!L108; nut face at OMi's overall length) | A20 HELD (2026-10-18): OMi overall length 2.47 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.51; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+        </is>
+      </c>
       <c r="BA22" t="inlineStr">
         <is>
           <t>1404-20-24</t>
@@ -4434,10 +4489,10 @@
         <v>2.61</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1547</v>
+        <v>1.22687</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.125</v>
       </c>
       <c r="E23" t="n">
         <v>0.93283</v>
@@ -4591,7 +4646,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -4607,7 +4667,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="C24" t="n">
         <v>1.22976</v>
@@ -4643,7 +4703,7 @@
         <v>0.86326</v>
       </c>
       <c r="N24" t="n">
-        <v>1.165</v>
+        <v>1.305</v>
       </c>
       <c r="O24" t="n">
         <v>0.8075</v>
@@ -4691,7 +4751,7 @@
         <v>0.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE24" t="n">
         <v>1.794</v>
@@ -4709,7 +4769,7 @@
         <v>0.96657</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AK24" t="n">
         <v>1.5</v>
@@ -4718,7 +4778,7 @@
         <v>1.1925</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
         <v>0.9575</v>
@@ -4768,6 +4828,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | Air-Way nut face to stem tip (W-L) 0.560 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_1404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1404_SW2.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="C2" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>0.40779</v>
@@ -721,7 +721,7 @@
         <v>0.35064</v>
       </c>
       <c r="N2" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0.304</v>
@@ -769,7 +769,7 @@
         <v>0.281</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AE2" t="n">
         <v>0.759</v>
@@ -787,7 +787,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AK2" t="n">
         <v>0.53</v>
@@ -845,12 +845,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X98 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R98 = 1 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.89) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.94 -&gt; OMi 1.89 (Items!L98; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R98, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.89 -&gt; Air-Way 1.94 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94 | Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -869,10 +869,10 @@
         <v>1.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.32447</v>
+        <v>0.28868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
         <v>0.19657</v>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X88 Side 2 ID = 0.110 (table had 0.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R88 = 0.562 (table had 0.5) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 0.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.562) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.15 -&gt; OMi 1.08 (Items!L88; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.11 (OMi, batch 14) -&gt; Air-Way 0.13 (0.13 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.5 -&gt; OMi 0.562 (Items!R88, M051) | A20 HELD (2026-10-18): OMi overall length 1.08 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.15; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.562 -&gt; Air-Way 0.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="C4" t="n">
-        <v>0.39722</v>
+        <v>0.36373</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E4" t="n">
         <v>0.19657</v>
@@ -1083,7 +1083,7 @@
         <v>0.16694</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="O4" t="n">
         <v>0.1825</v>
@@ -1131,7 +1131,7 @@
         <v>0.1485</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AE4" t="n">
         <v>0.481</v>
@@ -1149,7 +1149,7 @@
         <v>0.28494</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
         <v>0.19</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X89 Side 2 ID = 0.21 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R89 = 0.688 (table had 0.63) [user 2026-10-18 A19]; W@HEX: Air-Way 1.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.24) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.25 -&gt; OMi 1.24 (Items!L89; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.19 (0.19 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R89, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.24 -&gt; Air-Way 1.25 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1228,13 +1228,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="C5" t="n">
-        <v>0.39722</v>
+        <v>0.36373</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E5" t="n">
         <v>0.26092</v>
@@ -1264,7 +1264,7 @@
         <v>0.21647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="O5" t="n">
         <v>0.129</v>
@@ -1312,7 +1312,7 @@
         <v>0.117</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AE5" t="n">
         <v>0.364</v>
@@ -1330,7 +1330,7 @@
         <v>0.21163</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK5" t="n">
         <v>0.28</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R90 = 0.688 (table had 0.63) [user 2026-10-18 A19]; W@HEX: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.33) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.34 -&gt; OMi 1.33 (Items!L90; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R90, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.33 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1412,10 +1412,10 @@
         <v>1.44</v>
       </c>
       <c r="C6" t="n">
-        <v>0.39722</v>
+        <v>0.36373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E6" t="n">
         <v>0.26092</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X91 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R91 = 0.688 (table had 0.63) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 0.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.688) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.44 -&gt; OMi 1.42 (Items!L91; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.63 -&gt; OMi 0.688 (Items!R91, M051) | A20 HELD (2026-10-18): OMi overall length 1.42 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 1.44; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.688 -&gt; Air-Way 0.63</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="C7" t="n">
         <v>0.46765</v>
@@ -1626,7 +1626,7 @@
         <v>0.21647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="O7" t="n">
         <v>0.2465</v>
@@ -1674,7 +1674,7 @@
         <v>0.211</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AE7" t="n">
         <v>0.612</v>
@@ -1692,7 +1692,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AK7" t="n">
         <v>0.28</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); W@HEX: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L92; nut face at OMi's overall length) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.52 -&gt; Air-Way 1.56 | Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>0.26092</v>
@@ -1807,7 +1807,7 @@
         <v>0.21647</v>
       </c>
       <c r="N8" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0.304</v>
@@ -1855,7 +1855,7 @@
         <v>0.281</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AE8" t="n">
         <v>0.759</v>
@@ -1873,7 +1873,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AK8" t="n">
         <v>0.28</v>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X93 Side 2 ID = 0.44 (table had 0.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R93 = 1.000 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L93; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.28 (0.28 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1.000 (Items!R93, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.7 -&gt; Air-Way 1.75 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94 | Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="C9" t="n">
         <v>0.43301</v>
@@ -1988,7 +1988,7 @@
         <v>0.28378</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="O9" t="n">
         <v>0.1825</v>
@@ -2036,7 +2036,7 @@
         <v>0.1485</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AE9" t="n">
         <v>0.481</v>
@@ -2054,7 +2054,7 @@
         <v>0.28494</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AK9" t="n">
         <v>0.41</v>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X94 Side 2 ID = 0.21 (table had 0.22) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.49) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.5 -&gt; OMi 1.49 (Items!L94; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.21 (OMi, batch 14) -&gt; Air-Way 0.22 (0.22 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.49 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="C10" t="n">
-        <v>0.50518</v>
+        <v>0.46765</v>
       </c>
       <c r="D10" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0.32823</v>
@@ -2169,7 +2169,7 @@
         <v>0.28378</v>
       </c>
       <c r="N10" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="O10" t="n">
         <v>0.2465</v>
@@ -2217,7 +2217,7 @@
         <v>0.211</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AE10" t="n">
         <v>0.612</v>
@@ -2235,7 +2235,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AK10" t="n">
         <v>0.41</v>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X95 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R95 = 0.875 (table had 0.81) [user 2026-10-18 A19]; W@HEX: Air-Way 1.56 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.56 -&gt; OMi 1.52 (Items!L95; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.81 -&gt; OMi 0.875 (Items!R95, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.52 -&gt; Air-Way 1.56 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81 | Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C11" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.32823</v>
@@ -2350,7 +2350,7 @@
         <v>0.28378</v>
       </c>
       <c r="N11" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0.304</v>
@@ -2398,7 +2398,7 @@
         <v>0.281</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AE11" t="n">
         <v>0.759</v>
@@ -2416,7 +2416,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AK11" t="n">
         <v>0.41</v>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X96 Side 2 ID = 0.44 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R96 = 1 (table had 0.94) [user 2026-10-18 A19]; W@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.75 -&gt; OMi 1.70 (Items!L96; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.41 (0.41 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 0.94 -&gt; OMi 1 (Items!R96, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.7 -&gt; Air-Way 1.75 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94 | Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="C12" t="n">
         <v>0.50807</v>
@@ -2531,7 +2531,7 @@
         <v>0.35064</v>
       </c>
       <c r="N12" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="O12" t="n">
         <v>0.2465</v>
@@ -2579,7 +2579,7 @@
         <v>0.211</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AE12" t="n">
         <v>0.612</v>
@@ -2597,7 +2597,7 @@
         <v>0.35044</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AK12" t="n">
         <v>0.53</v>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X97 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X97 Side 2 ID = 0.32 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.77) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.81 -&gt; OMi 1.77 (Items!L97; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.32 (OMi, batch 14) -&gt; Air-Way 0.33 (0.33 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.77 -&gt; Air-Way 1.81 | Air-Way nut face to stem tip (W-L) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -2676,13 +2676,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.65241</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E13" t="n">
         <v>0.40779</v>
@@ -2712,7 +2712,7 @@
         <v>0.35064</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="O13" t="n">
         <v>0.389</v>
@@ -2760,7 +2760,7 @@
         <v>0.375</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AE13" t="n">
         <v>0.97</v>
@@ -2778,7 +2778,7 @@
         <v>0.54214</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AK13" t="n">
         <v>0.53</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X99 Side 2 ID = 0.61 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R99 = 1.250 (table had 1.13) [user 2026-10-18 A19]; W@HEX: Air-Way 2.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.09) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051) | Air-Way nut face to stem tip (W-L) 0.360 vs Brennan 0.330: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.09 (Items!L99; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.53 (0.53 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R99, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.09 -&gt; Air-Way 2.06 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.25 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2893,7 +2893,7 @@
         <v>0.45527</v>
       </c>
       <c r="N14" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>0.304</v>
@@ -2941,7 +2941,7 @@
         <v>0.281</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AE14" t="n">
         <v>0.759</v>
@@ -2959,7 +2959,7 @@
         <v>0.43664</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AK14" t="n">
         <v>0.72</v>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X100 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X100 Side 2 ID = 0.44 (table had 0.45) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 1.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.93) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | Air-Way nut face to stem tip (W-L) 0.310 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 1.95 -&gt; OMi 1.93 (Items!L100; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.44 (OMi, batch 14) -&gt; Air-Way 0.45 (0.45 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 1.93 -&gt; Air-Way 1.95 | Air-Way nut face to stem tip (W-L) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.65241</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E15" t="n">
         <v>0.51241</v>
@@ -3074,7 +3074,7 @@
         <v>0.45527</v>
       </c>
       <c r="N15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="O15" t="n">
         <v>0.389</v>
@@ -3122,7 +3122,7 @@
         <v>0.375</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="AE15" t="n">
         <v>0.97</v>
@@ -3140,7 +3140,7 @@
         <v>0.54214</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AK15" t="n">
         <v>0.72</v>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!S101 Side 1 ID = 0.610 (table had 0.72); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X101 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R101 = 1.250 (table had 1.13) [user 2026-10-18 A19]; W@HEX: Air-Way 2.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051) | Air-Way nut face to stem tip (W-L) 0.370 vs Brennan 0.330: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.06 -&gt; OMi 2.10 (Items!L101; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A21 (user 2026-10-18): D2@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 8 (D2))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.13 -&gt; OMi 1.250 (Items!R101, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.1 -&gt; Air-Way 2.06 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.25 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="C16" t="n">
         <v>0.86603</v>
@@ -3255,7 +3255,7 @@
         <v>0.45527</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="O16" t="n">
         <v>0.525</v>
@@ -3303,7 +3303,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="AE16" t="n">
         <v>1.211</v>
@@ -3321,7 +3321,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AK16" t="n">
         <v>0.72</v>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X102 Side 2 ID = 0.78 (table had 0.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X102 Side 2 ID = 0.78 (table had 0.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.18 -&gt; OMi 2.16 (Items!L102; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.72 (0.72 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.16 -&gt; Air-Way 2.18 | Air-Way nut face to stem tip (W-L) 0.370 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -3403,10 +3403,10 @@
         <v>2.31</v>
       </c>
       <c r="C17" t="n">
-        <v>0.86603</v>
+        <v>0.79674</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="E17" t="n">
         <v>0.6415999999999999</v>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X103 Side 2 ID = 0.61 (table had 0.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R103 = 1.500 (table had 1.38) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 1.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.31 -&gt; OMi 2.29 (Items!L103; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.61 (OMi, batch 14) -&gt; Air-Way 0.63 (0.63 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.38 -&gt; OMi 1.500 (Items!R103, M051) | A20 HELD (2026-10-18): OMi overall length 2.29 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.31; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.5 -&gt; Air-Way 1.38</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="C18" t="n">
         <v>0.86603</v>
@@ -3617,7 +3617,7 @@
         <v>0.57203</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="O18" t="n">
         <v>0.525</v>
@@ -3665,7 +3665,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="AE18" t="n">
         <v>1.211</v>
@@ -3683,7 +3683,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AK18" t="n">
         <v>0.9399999999999999</v>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X104 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X104 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D)))</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.35 (Items!L104; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.35 -&gt; Air-Way 2.38 | Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="C19" t="n">
-        <v>1.08253</v>
+        <v>1.01036</v>
       </c>
       <c r="D19" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0.6415999999999999</v>
@@ -3798,7 +3798,7 @@
         <v>0.57203</v>
       </c>
       <c r="N19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O19" t="n">
         <v>0.695</v>
@@ -3846,7 +3846,7 @@
         <v>0.6405</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="AE19" t="n">
         <v>1.555</v>
@@ -3864,7 +3864,7 @@
         <v>0.84707</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AK19" t="n">
         <v>0.9399999999999999</v>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R105 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.46 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.47) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051) | Air-Way nut face to stem tip (W-L) 0.440 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.46 -&gt; OMi 2.47 (Items!L105; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R105, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.47 -&gt; Air-Way 2.46 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="C20" t="n">
-        <v>1.08253</v>
+        <v>1.01036</v>
       </c>
       <c r="D20" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0.81335</v>
@@ -3979,7 +3979,7 @@
         <v>0.74378</v>
       </c>
       <c r="N20" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="O20" t="n">
         <v>0.525</v>
@@ -4027,7 +4027,7 @@
         <v>0.4845</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AE20" t="n">
         <v>1.211</v>
@@ -4045,7 +4045,7 @@
         <v>0.6750699999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AK20" t="n">
         <v>1.25</v>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X106 Side 2 ID = 0.78 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R106 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051) | Air-Way nut face to stem tip (W-L) 0.400 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.38 -&gt; OMi 2.40 (Items!L106; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 0.78 (OMi, batch 14) -&gt; Air-Way 0.84 (0.84 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R106, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.4 -&gt; Air-Way 2.38 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75 | Air-Way nut face to stem tip (W-L) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24)</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="C21" t="n">
-        <v>1.08253</v>
+        <v>1.01036</v>
       </c>
       <c r="D21" t="n">
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0.81335</v>
@@ -4160,7 +4160,7 @@
         <v>0.74378</v>
       </c>
       <c r="N21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="O21" t="n">
         <v>0.695</v>
@@ -4208,7 +4208,7 @@
         <v>0.6405</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AE21" t="n">
         <v>1.555</v>
@@ -4226,7 +4226,7 @@
         <v>0.84707</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AK21" t="n">
         <v>1.25</v>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R107 = 1.875 (table had 1.75) [user 2026-10-18 A19]; W@HEX: Air-Way 2.49 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.52) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051) | Air-Way nut face to stem tip (W-L) 0.460 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.49 -&gt; OMi 2.52 (Items!L107; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 1.75 -&gt; OMi 1.875 (Items!R107, M051) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.52 -&gt; Air-Way 2.49 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.875 -&gt; Air-Way 1.75</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -4489,10 +4489,10 @@
         <v>2.61</v>
       </c>
       <c r="C23" t="n">
-        <v>1.22687</v>
+        <v>1.1547</v>
       </c>
       <c r="D23" t="n">
-        <v>2.125</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0.93283</v>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R109 = 2.125 (table had 2) [user 2026-10-18 A19]; C1HEX@HEX: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.125) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.61 -&gt; OMi 2.54 (Items!L109; nut face at OMi's overall length) | A19 (user 2026-10-18, group 3 open): C1HEX@HEX 2 -&gt; OMi 2.125 (Items!R109, M051) | A20 HELD (2026-10-18): OMi overall length 2.54 as nut face breaks the measured NPSM swivel (W-L out of range; OMi gives no stem-tip length to pair) -&gt; kept at Air-Way W 2.61; user 2026-10-18: keep Air-Way W, reported to OMi (10_DRAWINGS/for_OMi_LATER) | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 2.125 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="C24" t="n">
         <v>1.22976</v>
@@ -4703,7 +4703,7 @@
         <v>0.86326</v>
       </c>
       <c r="N24" t="n">
-        <v>1.305</v>
+        <v>1.165</v>
       </c>
       <c r="O24" t="n">
         <v>0.8075</v>
@@ -4751,7 +4751,7 @@
         <v>0.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="AE24" t="n">
         <v>1.794</v>
@@ -4769,7 +4769,7 @@
         <v>0.96657</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="AK24" t="n">
         <v>1.5</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
+          <t>Air-Way s55 only (double-pass 27 rows); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X110 Side 2 ID = 1.25 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; W@HEX: Air-Way 2.55 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (Brennan 1404-08-08: 0.75 = the 5404 value; its internal 30deg tip chamfer NOT modelled); W = pipe tip to the nut face (overall), L = pipe tip to the stem tip; body hex C(1), nut hex C(2) (Air-Way); female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, body face at the measured distance behind the stem tip (Brennan); NUT FACE AT AIR-WAY W AND STEM TIP AT AIR-WAY L (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); bore D2 (pipe side) / D (stem side) stepped at the body-hex mid-plane (Brennan 1404-08-08 step at the hex mid-plane too)</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | Air-Way nut face to stem tip (W-L) 0.560 vs Brennan 0.420: nut placed at Air-Way W (user decision 2026-09-24)</t>
+          <t>A20 (user 2026-10-18): W@HEX 2.55 -&gt; OMi 2.69 (Items!L110; nut face at OMi's overall length) | A21 (user 2026-10-18): D@BORE 1.25 (OMi, batch 14) -&gt; Air-Way 1.26 (1.26 (07_RAW_EXTRACTS\1404.csv col 9 (D))) | 2026-10-20 Air-Way first: W@HEX OMi/Brennan 2.69 -&gt; Air-Way 2.55</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
